--- a/artfynd/A 27907-2024 artfynd.xlsx
+++ b/artfynd/A 27907-2024 artfynd.xlsx
@@ -1912,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119640345</v>
+        <v>119640333</v>
       </c>
       <c r="B13" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,21 +1928,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509355</v>
+        <v>509193</v>
       </c>
       <c r="R13" t="n">
-        <v>7003265</v>
+        <v>7003303</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119640333</v>
+        <v>119640345</v>
       </c>
       <c r="B14" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2039,21 +2039,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509193</v>
+        <v>509355</v>
       </c>
       <c r="R14" t="n">
-        <v>7003303</v>
+        <v>7003265</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119640319</v>
+        <v>119640326</v>
       </c>
       <c r="B28" t="n">
-        <v>79115</v>
+        <v>91856</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>2059</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509150</v>
+        <v>509099</v>
       </c>
       <c r="R28" t="n">
-        <v>7003149</v>
+        <v>7003219</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3691,14 +3691,6 @@
       <c r="AI28" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
-        </is>
-      </c>
-      <c r="AN28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov skorstenshögstubbe</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3720,10 +3712,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119640326</v>
+        <v>119640313</v>
       </c>
       <c r="B29" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3736,21 +3728,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3760,10 +3752,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509099</v>
+        <v>509208</v>
       </c>
       <c r="R29" t="n">
-        <v>7003219</v>
+        <v>7003162</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3831,10 +3823,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119640313</v>
+        <v>119640319</v>
       </c>
       <c r="B30" t="n">
-        <v>91834</v>
+        <v>79115</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3847,21 +3839,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4362</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3871,10 +3863,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509208</v>
+        <v>509150</v>
       </c>
       <c r="R30" t="n">
-        <v>7003162</v>
+        <v>7003149</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3921,6 +3913,14 @@
       <c r="AI30" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov skorstenshögstubbe</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 27907-2024 artfynd.xlsx
+++ b/artfynd/A 27907-2024 artfynd.xlsx
@@ -4497,10 +4497,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119640323</v>
+        <v>119640311</v>
       </c>
       <c r="B36" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4513,21 +4513,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>509110</v>
+        <v>509147</v>
       </c>
       <c r="R36" t="n">
-        <v>7003127</v>
+        <v>7003106</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4608,10 +4608,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119640311</v>
+        <v>119640323</v>
       </c>
       <c r="B37" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4624,21 +4624,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4648,10 +4648,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>509147</v>
+        <v>509110</v>
       </c>
       <c r="R37" t="n">
-        <v>7003106</v>
+        <v>7003127</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 27907-2024 artfynd.xlsx
+++ b/artfynd/A 27907-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119640308</v>
+        <v>119640310</v>
       </c>
       <c r="B2" t="n">
-        <v>89230</v>
+        <v>91834</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1596</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509079</v>
+        <v>509021</v>
       </c>
       <c r="R2" t="n">
-        <v>7003062</v>
+        <v>7003112</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119640305</v>
+        <v>119640306</v>
       </c>
       <c r="B3" t="n">
-        <v>78171</v>
+        <v>91832</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509076</v>
+        <v>509070</v>
       </c>
       <c r="R3" t="n">
-        <v>7003011</v>
+        <v>7003029</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,14 +876,6 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal hård tallåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -905,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119640306</v>
+        <v>119640333</v>
       </c>
       <c r="B4" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -945,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509070</v>
+        <v>509193</v>
       </c>
       <c r="R4" t="n">
-        <v>7003029</v>
+        <v>7003303</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119640310</v>
+        <v>119640323</v>
       </c>
       <c r="B5" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509021</v>
+        <v>509110</v>
       </c>
       <c r="R5" t="n">
-        <v>7003112</v>
+        <v>7003127</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119640318</v>
+        <v>119640311</v>
       </c>
       <c r="B6" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509193</v>
+        <v>509147</v>
       </c>
       <c r="R6" t="n">
-        <v>7003189</v>
+        <v>7003106</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119640303</v>
+        <v>119640304</v>
       </c>
       <c r="B7" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1278,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509034</v>
+        <v>509047</v>
       </c>
       <c r="R7" t="n">
-        <v>7002954</v>
+        <v>7002984</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119640316</v>
+        <v>119640334</v>
       </c>
       <c r="B8" t="n">
         <v>91884</v>
@@ -1389,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509176</v>
+        <v>509212</v>
       </c>
       <c r="R8" t="n">
-        <v>7003222</v>
+        <v>7003317</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119640329</v>
+        <v>119640321</v>
       </c>
       <c r="B9" t="n">
-        <v>78171</v>
+        <v>91834</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,21 +1468,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1500,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509119</v>
+        <v>509129</v>
       </c>
       <c r="R9" t="n">
-        <v>7003280</v>
+        <v>7003175</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,14 +1542,6 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
-        </is>
-      </c>
-      <c r="AN9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal lumpad talltopp</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1579,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119640314</v>
+        <v>119640350</v>
       </c>
       <c r="B10" t="n">
         <v>91884</v>
@@ -1619,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509280</v>
+        <v>509371</v>
       </c>
       <c r="R10" t="n">
-        <v>7003207</v>
+        <v>7003152</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1652,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på sandig morän med lav</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1690,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119640342</v>
+        <v>119640305</v>
       </c>
       <c r="B11" t="n">
-        <v>91834</v>
+        <v>78171</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1706,21 +1690,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509303</v>
+        <v>509076</v>
       </c>
       <c r="R11" t="n">
-        <v>7003323</v>
+        <v>7003011</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1780,6 +1764,14 @@
       <c r="AI11" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal hård tallåga</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1801,7 +1793,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119640334</v>
+        <v>119640303</v>
       </c>
       <c r="B12" t="n">
         <v>91884</v>
@@ -1841,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509212</v>
+        <v>509034</v>
       </c>
       <c r="R12" t="n">
-        <v>7003317</v>
+        <v>7002954</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1912,10 +1904,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119640333</v>
+        <v>119640342</v>
       </c>
       <c r="B13" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,21 +1920,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509193</v>
+        <v>509303</v>
       </c>
       <c r="R13" t="n">
-        <v>7003303</v>
+        <v>7003323</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,10 +2015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119640345</v>
+        <v>119640314</v>
       </c>
       <c r="B14" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2039,21 +2031,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509355</v>
+        <v>509280</v>
       </c>
       <c r="R14" t="n">
-        <v>7003265</v>
+        <v>7003207</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119640331</v>
+        <v>119640308</v>
       </c>
       <c r="B15" t="n">
-        <v>91856</v>
+        <v>89230</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2146,25 +2138,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2059</v>
+        <v>1596</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2174,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509112</v>
+        <v>509079</v>
       </c>
       <c r="R15" t="n">
-        <v>7003283</v>
+        <v>7003062</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,7 +2237,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119640343</v>
+        <v>119640320</v>
       </c>
       <c r="B16" t="n">
         <v>91856</v>
@@ -2285,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509352</v>
+        <v>509134</v>
       </c>
       <c r="R16" t="n">
-        <v>7003312</v>
+        <v>7003179</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2356,7 +2348,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119640328</v>
+        <v>119640322</v>
       </c>
       <c r="B17" t="n">
         <v>91834</v>
@@ -2396,10 +2388,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509119</v>
+        <v>509105</v>
       </c>
       <c r="R17" t="n">
-        <v>7003223</v>
+        <v>7003126</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2467,10 +2459,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119640350</v>
+        <v>119640335</v>
       </c>
       <c r="B18" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,21 +2475,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509371</v>
+        <v>509211</v>
       </c>
       <c r="R18" t="n">
-        <v>7003152</v>
+        <v>7003306</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2556,7 +2548,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>140-årig tallskog på sandig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2578,10 +2570,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119640338</v>
+        <v>119640318</v>
       </c>
       <c r="B19" t="n">
-        <v>78171</v>
+        <v>91834</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2594,21 +2586,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2618,10 +2610,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509266</v>
+        <v>509193</v>
       </c>
       <c r="R19" t="n">
-        <v>7003365</v>
+        <v>7003189</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2668,14 +2660,6 @@
       <c r="AI19" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
-        </is>
-      </c>
-      <c r="AN19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal rest av tallåga</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2697,10 +2681,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119640309</v>
+        <v>119640328</v>
       </c>
       <c r="B20" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2713,21 +2697,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2737,10 +2721,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509034</v>
+        <v>509119</v>
       </c>
       <c r="R20" t="n">
-        <v>7003097</v>
+        <v>7003223</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2808,10 +2792,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119640307</v>
+        <v>119640351</v>
       </c>
       <c r="B21" t="n">
-        <v>91856</v>
+        <v>89252</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2820,25 +2804,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2848,10 +2832,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509057</v>
+        <v>509378</v>
       </c>
       <c r="R21" t="n">
-        <v>7003066</v>
+        <v>7003167</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2897,7 +2881,15 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på sandig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2919,10 +2911,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119640335</v>
+        <v>119640325</v>
       </c>
       <c r="B22" t="n">
-        <v>91834</v>
+        <v>89252</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2931,25 +2923,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2959,10 +2951,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509211</v>
+        <v>509096</v>
       </c>
       <c r="R22" t="n">
-        <v>7003306</v>
+        <v>7003215</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3030,10 +3022,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119640341</v>
+        <v>119640317</v>
       </c>
       <c r="B23" t="n">
-        <v>91852</v>
+        <v>91856</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3042,25 +3034,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3070,10 +3062,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>509269</v>
+        <v>509191</v>
       </c>
       <c r="R23" t="n">
-        <v>7003308</v>
+        <v>7003220</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3141,10 +3133,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119640352</v>
+        <v>119640313</v>
       </c>
       <c r="B24" t="n">
-        <v>78171</v>
+        <v>91834</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3157,21 +3149,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3181,10 +3173,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>509378</v>
+        <v>509208</v>
       </c>
       <c r="R24" t="n">
-        <v>7003167</v>
+        <v>7003162</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3230,15 +3222,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>140-årig tallskog på sandig morän med lav</t>
-        </is>
-      </c>
-      <c r="AN24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal hård tallåga</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3260,7 +3244,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119640332</v>
+        <v>119640353</v>
       </c>
       <c r="B25" t="n">
         <v>91834</v>
@@ -3300,10 +3284,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509129</v>
+        <v>509374</v>
       </c>
       <c r="R25" t="n">
-        <v>7003296</v>
+        <v>7003152</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3349,7 +3333,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på sandig morän med lav</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3371,10 +3355,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119640325</v>
+        <v>119640307</v>
       </c>
       <c r="B26" t="n">
-        <v>89252</v>
+        <v>91856</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3383,25 +3367,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3411,10 +3395,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509096</v>
+        <v>509057</v>
       </c>
       <c r="R26" t="n">
-        <v>7003215</v>
+        <v>7003066</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3482,10 +3466,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119640351</v>
+        <v>119640309</v>
       </c>
       <c r="B27" t="n">
-        <v>89252</v>
+        <v>91856</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3494,25 +3478,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3522,10 +3506,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509378</v>
+        <v>509034</v>
       </c>
       <c r="R27" t="n">
-        <v>7003167</v>
+        <v>7003097</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3571,15 +3555,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>140-årig tallskog på sandig morän med lav</t>
-        </is>
-      </c>
-      <c r="AN27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3601,10 +3577,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119640326</v>
+        <v>119640341</v>
       </c>
       <c r="B28" t="n">
-        <v>91856</v>
+        <v>91852</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3613,25 +3589,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3641,10 +3617,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509099</v>
+        <v>509269</v>
       </c>
       <c r="R28" t="n">
-        <v>7003219</v>
+        <v>7003308</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3712,10 +3688,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119640313</v>
+        <v>119640338</v>
       </c>
       <c r="B29" t="n">
-        <v>91834</v>
+        <v>78171</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3728,21 +3704,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3752,10 +3728,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509208</v>
+        <v>509266</v>
       </c>
       <c r="R29" t="n">
-        <v>7003162</v>
+        <v>7003365</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3802,6 +3778,14 @@
       <c r="AI29" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal rest av tallåga</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3942,10 +3926,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119640353</v>
+        <v>119640345</v>
       </c>
       <c r="B31" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3958,21 +3942,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3982,10 +3966,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509374</v>
+        <v>509355</v>
       </c>
       <c r="R31" t="n">
-        <v>7003152</v>
+        <v>7003265</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4031,7 +4015,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>140-årig tallskog på sandig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4053,10 +4037,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119640321</v>
+        <v>119640312</v>
       </c>
       <c r="B32" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4069,21 +4053,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4093,10 +4077,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509129</v>
+        <v>509178</v>
       </c>
       <c r="R32" t="n">
-        <v>7003175</v>
+        <v>7003099</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4164,10 +4148,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119640317</v>
+        <v>119640352</v>
       </c>
       <c r="B33" t="n">
-        <v>91856</v>
+        <v>78171</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4180,21 +4164,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4204,10 +4188,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>509191</v>
+        <v>509378</v>
       </c>
       <c r="R33" t="n">
-        <v>7003220</v>
+        <v>7003167</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4253,7 +4237,15 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på sandig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal hård tallåga</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4275,7 +4267,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119640320</v>
+        <v>119640331</v>
       </c>
       <c r="B34" t="n">
         <v>91856</v>
@@ -4315,10 +4307,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>509134</v>
+        <v>509112</v>
       </c>
       <c r="R34" t="n">
-        <v>7003179</v>
+        <v>7003283</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4386,10 +4378,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119640304</v>
+        <v>119640339</v>
       </c>
       <c r="B35" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4402,21 +4394,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4418,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>509047</v>
+        <v>509247</v>
       </c>
       <c r="R35" t="n">
-        <v>7002984</v>
+        <v>7003393</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4497,10 +4489,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119640311</v>
+        <v>119640326</v>
       </c>
       <c r="B36" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4513,21 +4505,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4537,10 +4529,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>509147</v>
+        <v>509099</v>
       </c>
       <c r="R36" t="n">
-        <v>7003106</v>
+        <v>7003219</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4608,10 +4600,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119640323</v>
+        <v>119640346</v>
       </c>
       <c r="B37" t="n">
-        <v>91856</v>
+        <v>91852</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4620,25 +4612,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4648,10 +4640,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>509110</v>
+        <v>509308</v>
       </c>
       <c r="R37" t="n">
-        <v>7003127</v>
+        <v>7003248</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4719,10 +4711,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119640339</v>
+        <v>119640332</v>
       </c>
       <c r="B38" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4735,21 +4727,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4759,10 +4751,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509247</v>
+        <v>509129</v>
       </c>
       <c r="R38" t="n">
-        <v>7003393</v>
+        <v>7003296</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4830,10 +4822,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119640347</v>
+        <v>119640315</v>
       </c>
       <c r="B39" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4846,21 +4838,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4870,10 +4862,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509319</v>
+        <v>509194</v>
       </c>
       <c r="R39" t="n">
-        <v>7003219</v>
+        <v>7003235</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4941,10 +4933,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119640348</v>
+        <v>119640316</v>
       </c>
       <c r="B40" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4957,21 +4949,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4981,10 +4973,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>509315</v>
+        <v>509176</v>
       </c>
       <c r="R40" t="n">
-        <v>7003198</v>
+        <v>7003222</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5052,10 +5044,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119640322</v>
+        <v>119640329</v>
       </c>
       <c r="B41" t="n">
-        <v>91834</v>
+        <v>78171</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5068,21 +5060,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5092,10 +5084,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>509105</v>
+        <v>509119</v>
       </c>
       <c r="R41" t="n">
-        <v>7003126</v>
+        <v>7003280</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5142,6 +5134,14 @@
       <c r="AI41" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal lumpad talltopp</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5163,10 +5163,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119640312</v>
+        <v>119640347</v>
       </c>
       <c r="B42" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5179,21 +5179,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>509178</v>
+        <v>509319</v>
       </c>
       <c r="R42" t="n">
-        <v>7003099</v>
+        <v>7003219</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5274,10 +5274,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119640315</v>
+        <v>119640343</v>
       </c>
       <c r="B43" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5290,21 +5290,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>509194</v>
+        <v>509352</v>
       </c>
       <c r="R43" t="n">
-        <v>7003235</v>
+        <v>7003312</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5385,10 +5385,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119640346</v>
+        <v>119640348</v>
       </c>
       <c r="B44" t="n">
-        <v>91852</v>
+        <v>91856</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5397,25 +5397,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5425,10 +5425,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>509308</v>
+        <v>509315</v>
       </c>
       <c r="R44" t="n">
-        <v>7003248</v>
+        <v>7003198</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 27907-2024 artfynd.xlsx
+++ b/artfynd/A 27907-2024 artfynd.xlsx
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119640334</v>
+        <v>119640321</v>
       </c>
       <c r="B8" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509212</v>
+        <v>509129</v>
       </c>
       <c r="R8" t="n">
-        <v>7003317</v>
+        <v>7003175</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119640321</v>
+        <v>119640350</v>
       </c>
       <c r="B9" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,21 +1468,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509129</v>
+        <v>509371</v>
       </c>
       <c r="R9" t="n">
-        <v>7003175</v>
+        <v>7003152</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på sandig morän med lav</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119640350</v>
+        <v>119640334</v>
       </c>
       <c r="B10" t="n">
         <v>91884</v>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509371</v>
+        <v>509212</v>
       </c>
       <c r="R10" t="n">
-        <v>7003152</v>
+        <v>7003317</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>140-årig tallskog på sandig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119640342</v>
+        <v>119640314</v>
       </c>
       <c r="B13" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1920,21 +1920,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509303</v>
+        <v>509280</v>
       </c>
       <c r="R13" t="n">
-        <v>7003323</v>
+        <v>7003207</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,10 +2015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119640314</v>
+        <v>119640308</v>
       </c>
       <c r="B14" t="n">
-        <v>91884</v>
+        <v>89230</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2027,25 +2027,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>1596</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509280</v>
+        <v>509079</v>
       </c>
       <c r="R14" t="n">
-        <v>7003207</v>
+        <v>7003062</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119640308</v>
+        <v>119640342</v>
       </c>
       <c r="B15" t="n">
-        <v>89230</v>
+        <v>91834</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,25 +2138,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1596</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509079</v>
+        <v>509303</v>
       </c>
       <c r="R15" t="n">
-        <v>7003062</v>
+        <v>7003323</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -3688,10 +3688,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119640338</v>
+        <v>119640319</v>
       </c>
       <c r="B29" t="n">
-        <v>78171</v>
+        <v>79115</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3704,21 +3704,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509266</v>
+        <v>509150</v>
       </c>
       <c r="R29" t="n">
-        <v>7003365</v>
+        <v>7003149</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal rest av tallåga</t>
+          <t>1 substratenheter # grov skorstenshögstubbe</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3807,10 +3807,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119640319</v>
+        <v>119640338</v>
       </c>
       <c r="B30" t="n">
-        <v>79115</v>
+        <v>78171</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3823,21 +3823,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509150</v>
+        <v>509266</v>
       </c>
       <c r="R30" t="n">
-        <v>7003149</v>
+        <v>7003365</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov skorstenshögstubbe</t>
+          <t>1 substratenheter # gammal rest av tallåga</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 27907-2024 artfynd.xlsx
+++ b/artfynd/A 27907-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119640310</v>
+        <v>119640329</v>
       </c>
       <c r="B2" t="n">
-        <v>91834</v>
+        <v>78171</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509021</v>
+        <v>509119</v>
       </c>
       <c r="R2" t="n">
-        <v>7003112</v>
+        <v>7003280</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,6 +765,14 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal lumpad talltopp</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119640306</v>
+        <v>119640348</v>
       </c>
       <c r="B3" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509070</v>
+        <v>509315</v>
       </c>
       <c r="R3" t="n">
-        <v>7003029</v>
+        <v>7003198</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1008,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119640323</v>
+        <v>119640345</v>
       </c>
       <c r="B5" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509110</v>
+        <v>509355</v>
       </c>
       <c r="R5" t="n">
-        <v>7003127</v>
+        <v>7003265</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119640311</v>
+        <v>119640341</v>
       </c>
       <c r="B6" t="n">
-        <v>91884</v>
+        <v>91852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1139,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509147</v>
+        <v>509269</v>
       </c>
       <c r="R6" t="n">
-        <v>7003106</v>
+        <v>7003308</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1238,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119640304</v>
+        <v>119640353</v>
       </c>
       <c r="B7" t="n">
         <v>91834</v>
@@ -1270,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509047</v>
+        <v>509374</v>
       </c>
       <c r="R7" t="n">
-        <v>7002984</v>
+        <v>7003152</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1327,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på sandig morän med lav</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1341,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119640321</v>
+        <v>119640317</v>
       </c>
       <c r="B8" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1365,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1381,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509129</v>
+        <v>509191</v>
       </c>
       <c r="R8" t="n">
-        <v>7003175</v>
+        <v>7003220</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119640350</v>
+        <v>119640319</v>
       </c>
       <c r="B9" t="n">
-        <v>91884</v>
+        <v>79115</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,21 +1476,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509371</v>
+        <v>509150</v>
       </c>
       <c r="R9" t="n">
-        <v>7003152</v>
+        <v>7003149</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1549,15 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>140-årig tallskog på sandig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov skorstenshögstubbe</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1563,10 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119640334</v>
+        <v>119640331</v>
       </c>
       <c r="B10" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,21 +1595,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1603,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509212</v>
+        <v>509112</v>
       </c>
       <c r="R10" t="n">
-        <v>7003317</v>
+        <v>7003283</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119640305</v>
+        <v>119640350</v>
       </c>
       <c r="B11" t="n">
-        <v>78171</v>
+        <v>91884</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,21 +1706,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>5449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1714,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509076</v>
+        <v>509371</v>
       </c>
       <c r="R11" t="n">
-        <v>7003011</v>
+        <v>7003152</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,15 +1779,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
-        </is>
-      </c>
-      <c r="AN11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal hård tallåga</t>
+          <t>140-årig tallskog på sandig morän med lav</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1793,10 +1801,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119640303</v>
+        <v>119640322</v>
       </c>
       <c r="B12" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,21 +1817,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1833,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509034</v>
+        <v>509105</v>
       </c>
       <c r="R12" t="n">
-        <v>7002954</v>
+        <v>7003126</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119640314</v>
+        <v>119640318</v>
       </c>
       <c r="B13" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1920,21 +1928,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1944,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509280</v>
+        <v>509193</v>
       </c>
       <c r="R13" t="n">
-        <v>7003207</v>
+        <v>7003189</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119640308</v>
+        <v>119640320</v>
       </c>
       <c r="B14" t="n">
-        <v>89230</v>
+        <v>91856</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2027,25 +2035,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1596</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2055,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509079</v>
+        <v>509134</v>
       </c>
       <c r="R14" t="n">
-        <v>7003062</v>
+        <v>7003179</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2126,10 +2134,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119640342</v>
+        <v>119640334</v>
       </c>
       <c r="B15" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2142,21 +2150,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2174,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509303</v>
+        <v>509212</v>
       </c>
       <c r="R15" t="n">
-        <v>7003323</v>
+        <v>7003317</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2237,7 +2245,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119640320</v>
+        <v>119640323</v>
       </c>
       <c r="B16" t="n">
         <v>91856</v>
@@ -2277,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509134</v>
+        <v>509110</v>
       </c>
       <c r="R16" t="n">
-        <v>7003179</v>
+        <v>7003127</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2348,7 +2356,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119640322</v>
+        <v>119640332</v>
       </c>
       <c r="B17" t="n">
         <v>91834</v>
@@ -2388,10 +2396,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509105</v>
+        <v>509129</v>
       </c>
       <c r="R17" t="n">
-        <v>7003126</v>
+        <v>7003296</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2570,10 +2578,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119640318</v>
+        <v>119640315</v>
       </c>
       <c r="B19" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2586,21 +2594,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2610,10 +2618,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509193</v>
+        <v>509194</v>
       </c>
       <c r="R19" t="n">
-        <v>7003189</v>
+        <v>7003235</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2681,7 +2689,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119640328</v>
+        <v>119640310</v>
       </c>
       <c r="B20" t="n">
         <v>91834</v>
@@ -2721,10 +2729,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509119</v>
+        <v>509021</v>
       </c>
       <c r="R20" t="n">
-        <v>7003223</v>
+        <v>7003112</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2792,10 +2800,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119640351</v>
+        <v>119640328</v>
       </c>
       <c r="B21" t="n">
-        <v>89252</v>
+        <v>91834</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2804,25 +2812,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2832,10 +2840,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509378</v>
+        <v>509119</v>
       </c>
       <c r="R21" t="n">
-        <v>7003167</v>
+        <v>7003223</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2881,15 +2889,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>140-årig tallskog på sandig morän med lav</t>
-        </is>
-      </c>
-      <c r="AN21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119640325</v>
+        <v>119640303</v>
       </c>
       <c r="B22" t="n">
-        <v>89252</v>
+        <v>91884</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2923,25 +2923,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6276</v>
+        <v>5449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509096</v>
+        <v>509034</v>
       </c>
       <c r="R22" t="n">
-        <v>7003215</v>
+        <v>7002954</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119640317</v>
+        <v>119640316</v>
       </c>
       <c r="B23" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3038,21 +3038,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>509191</v>
+        <v>509176</v>
       </c>
       <c r="R23" t="n">
-        <v>7003220</v>
+        <v>7003222</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119640313</v>
+        <v>119640314</v>
       </c>
       <c r="B24" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3149,21 +3149,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>509208</v>
+        <v>509280</v>
       </c>
       <c r="R24" t="n">
-        <v>7003162</v>
+        <v>7003207</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119640353</v>
+        <v>119640338</v>
       </c>
       <c r="B25" t="n">
-        <v>91834</v>
+        <v>78171</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3260,21 +3260,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509374</v>
+        <v>509266</v>
       </c>
       <c r="R25" t="n">
-        <v>7003152</v>
+        <v>7003365</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3333,7 +3333,15 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>140-årig tallskog på sandig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal rest av tallåga</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3355,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119640307</v>
+        <v>119640352</v>
       </c>
       <c r="B26" t="n">
-        <v>91856</v>
+        <v>78171</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3371,21 +3379,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3395,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509057</v>
+        <v>509378</v>
       </c>
       <c r="R26" t="n">
-        <v>7003066</v>
+        <v>7003167</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3444,7 +3452,15 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på sandig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal hård tallåga</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3466,7 +3482,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119640309</v>
+        <v>119640343</v>
       </c>
       <c r="B27" t="n">
         <v>91856</v>
@@ -3506,10 +3522,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509034</v>
+        <v>509352</v>
       </c>
       <c r="R27" t="n">
-        <v>7003097</v>
+        <v>7003312</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3577,10 +3593,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119640341</v>
+        <v>119640347</v>
       </c>
       <c r="B28" t="n">
-        <v>91852</v>
+        <v>91856</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3589,25 +3605,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3617,10 +3633,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509269</v>
+        <v>509319</v>
       </c>
       <c r="R28" t="n">
-        <v>7003308</v>
+        <v>7003219</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3688,10 +3704,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119640319</v>
+        <v>119640346</v>
       </c>
       <c r="B29" t="n">
-        <v>79115</v>
+        <v>91852</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3700,25 +3716,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>4366</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3728,10 +3744,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509150</v>
+        <v>509308</v>
       </c>
       <c r="R29" t="n">
-        <v>7003149</v>
+        <v>7003248</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3778,14 +3794,6 @@
       <c r="AI29" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
-        </is>
-      </c>
-      <c r="AN29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov skorstenshögstubbe</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3807,10 +3815,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119640338</v>
+        <v>119640339</v>
       </c>
       <c r="B30" t="n">
-        <v>78171</v>
+        <v>91856</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3823,21 +3831,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3847,10 +3855,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509266</v>
+        <v>509247</v>
       </c>
       <c r="R30" t="n">
-        <v>7003365</v>
+        <v>7003393</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3897,14 +3905,6 @@
       <c r="AI30" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
-        </is>
-      </c>
-      <c r="AN30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal rest av tallåga</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119640345</v>
+        <v>119640313</v>
       </c>
       <c r="B31" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3942,21 +3942,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509355</v>
+        <v>509208</v>
       </c>
       <c r="R31" t="n">
-        <v>7003265</v>
+        <v>7003162</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4037,7 +4037,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119640312</v>
+        <v>119640306</v>
       </c>
       <c r="B32" t="n">
         <v>91832</v>
@@ -4077,10 +4077,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509178</v>
+        <v>509070</v>
       </c>
       <c r="R32" t="n">
-        <v>7003099</v>
+        <v>7003029</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4148,7 +4148,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119640352</v>
+        <v>119640305</v>
       </c>
       <c r="B33" t="n">
         <v>78171</v>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>509378</v>
+        <v>509076</v>
       </c>
       <c r="R33" t="n">
-        <v>7003167</v>
+        <v>7003011</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>140-årig tallskog på sandig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AN33" t="n">
@@ -4267,10 +4267,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119640331</v>
+        <v>119640321</v>
       </c>
       <c r="B34" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4283,21 +4283,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>509112</v>
+        <v>509129</v>
       </c>
       <c r="R34" t="n">
-        <v>7003283</v>
+        <v>7003175</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119640339</v>
+        <v>119640304</v>
       </c>
       <c r="B35" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4394,21 +4394,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>509247</v>
+        <v>509047</v>
       </c>
       <c r="R35" t="n">
-        <v>7003393</v>
+        <v>7002984</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4489,10 +4489,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119640326</v>
+        <v>119640351</v>
       </c>
       <c r="B36" t="n">
-        <v>91856</v>
+        <v>89252</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4501,25 +4501,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>509099</v>
+        <v>509378</v>
       </c>
       <c r="R36" t="n">
-        <v>7003219</v>
+        <v>7003167</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4578,7 +4578,15 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på sandig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4600,10 +4608,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119640346</v>
+        <v>119640325</v>
       </c>
       <c r="B37" t="n">
-        <v>91852</v>
+        <v>89252</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4612,25 +4620,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4366</v>
+        <v>6276</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4640,10 +4648,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>509308</v>
+        <v>509096</v>
       </c>
       <c r="R37" t="n">
-        <v>7003248</v>
+        <v>7003215</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4711,10 +4719,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119640332</v>
+        <v>119640311</v>
       </c>
       <c r="B38" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4727,21 +4735,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4751,10 +4759,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509129</v>
+        <v>509147</v>
       </c>
       <c r="R38" t="n">
-        <v>7003296</v>
+        <v>7003106</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4822,10 +4830,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119640315</v>
+        <v>119640326</v>
       </c>
       <c r="B39" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4838,21 +4846,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4862,10 +4870,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509194</v>
+        <v>509099</v>
       </c>
       <c r="R39" t="n">
-        <v>7003235</v>
+        <v>7003219</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4933,10 +4941,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119640316</v>
+        <v>119640309</v>
       </c>
       <c r="B40" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4949,21 +4957,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4973,10 +4981,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>509176</v>
+        <v>509034</v>
       </c>
       <c r="R40" t="n">
-        <v>7003222</v>
+        <v>7003097</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5044,10 +5052,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119640329</v>
+        <v>119640312</v>
       </c>
       <c r="B41" t="n">
-        <v>78171</v>
+        <v>91832</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5060,21 +5068,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5084,10 +5092,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>509119</v>
+        <v>509178</v>
       </c>
       <c r="R41" t="n">
-        <v>7003280</v>
+        <v>7003099</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5134,14 +5142,6 @@
       <c r="AI41" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
-        </is>
-      </c>
-      <c r="AN41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal lumpad talltopp</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119640347</v>
+        <v>119640307</v>
       </c>
       <c r="B42" t="n">
         <v>91856</v>
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>509319</v>
+        <v>509057</v>
       </c>
       <c r="R42" t="n">
-        <v>7003219</v>
+        <v>7003066</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5274,10 +5274,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119640343</v>
+        <v>119640342</v>
       </c>
       <c r="B43" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5290,21 +5290,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>509352</v>
+        <v>509303</v>
       </c>
       <c r="R43" t="n">
-        <v>7003312</v>
+        <v>7003323</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5385,10 +5385,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119640348</v>
+        <v>119640308</v>
       </c>
       <c r="B44" t="n">
-        <v>91856</v>
+        <v>89230</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5397,25 +5397,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2059</v>
+        <v>1596</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5425,10 +5425,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>509315</v>
+        <v>509079</v>
       </c>
       <c r="R44" t="n">
-        <v>7003198</v>
+        <v>7003062</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 27907-2024 artfynd.xlsx
+++ b/artfynd/A 27907-2024 artfynd.xlsx
@@ -3815,10 +3815,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119640339</v>
+        <v>119640305</v>
       </c>
       <c r="B30" t="n">
-        <v>91856</v>
+        <v>78171</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3831,21 +3831,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3855,10 +3855,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509247</v>
+        <v>509076</v>
       </c>
       <c r="R30" t="n">
-        <v>7003393</v>
+        <v>7003011</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3905,6 +3905,14 @@
       <c r="AI30" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal hård tallåga</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3926,10 +3934,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119640313</v>
+        <v>119640339</v>
       </c>
       <c r="B31" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3942,21 +3950,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3966,10 +3974,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509208</v>
+        <v>509247</v>
       </c>
       <c r="R31" t="n">
-        <v>7003162</v>
+        <v>7003393</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4037,10 +4045,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119640306</v>
+        <v>119640313</v>
       </c>
       <c r="B32" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4053,21 +4061,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4077,10 +4085,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509070</v>
+        <v>509208</v>
       </c>
       <c r="R32" t="n">
-        <v>7003029</v>
+        <v>7003162</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4148,10 +4156,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119640305</v>
+        <v>119640306</v>
       </c>
       <c r="B33" t="n">
-        <v>78171</v>
+        <v>91832</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4164,21 +4172,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4188,10 +4196,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>509076</v>
+        <v>509070</v>
       </c>
       <c r="R33" t="n">
-        <v>7003011</v>
+        <v>7003029</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4238,14 +4246,6 @@
       <c r="AI33" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
-        </is>
-      </c>
-      <c r="AN33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal hård tallåga</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119640304</v>
+        <v>119640351</v>
       </c>
       <c r="B35" t="n">
-        <v>91834</v>
+        <v>89252</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4390,25 +4390,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>509047</v>
+        <v>509378</v>
       </c>
       <c r="R35" t="n">
-        <v>7002984</v>
+        <v>7003167</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4467,7 +4467,15 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på sandig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4489,7 +4497,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119640351</v>
+        <v>119640325</v>
       </c>
       <c r="B36" t="n">
         <v>89252</v>
@@ -4529,10 +4537,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>509378</v>
+        <v>509096</v>
       </c>
       <c r="R36" t="n">
-        <v>7003167</v>
+        <v>7003215</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4578,15 +4586,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>140-årig tallskog på sandig morän med lav</t>
-        </is>
-      </c>
-      <c r="AN36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4608,10 +4608,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119640325</v>
+        <v>119640311</v>
       </c>
       <c r="B37" t="n">
-        <v>89252</v>
+        <v>91884</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4620,25 +4620,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6276</v>
+        <v>5449</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4648,10 +4648,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>509096</v>
+        <v>509147</v>
       </c>
       <c r="R37" t="n">
-        <v>7003215</v>
+        <v>7003106</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4719,10 +4719,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119640311</v>
+        <v>119640304</v>
       </c>
       <c r="B38" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4735,21 +4735,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4759,10 +4759,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509147</v>
+        <v>509047</v>
       </c>
       <c r="R38" t="n">
-        <v>7003106</v>
+        <v>7002984</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 27907-2024 artfynd.xlsx
+++ b/artfynd/A 27907-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119640329</v>
+        <v>119640303</v>
       </c>
       <c r="B2" t="n">
-        <v>78171</v>
+        <v>91884</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509119</v>
+        <v>509034</v>
       </c>
       <c r="R2" t="n">
-        <v>7003280</v>
+        <v>7002954</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,14 +765,6 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal lumpad talltopp</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119640348</v>
+        <v>119640339</v>
       </c>
       <c r="B3" t="n">
         <v>91856</v>
@@ -834,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509315</v>
+        <v>509247</v>
       </c>
       <c r="R3" t="n">
-        <v>7003198</v>
+        <v>7003393</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119640333</v>
+        <v>119640328</v>
       </c>
       <c r="B4" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -945,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509193</v>
+        <v>509119</v>
       </c>
       <c r="R4" t="n">
-        <v>7003303</v>
+        <v>7003223</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119640345</v>
+        <v>119640341</v>
       </c>
       <c r="B5" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509355</v>
+        <v>509269</v>
       </c>
       <c r="R5" t="n">
-        <v>7003265</v>
+        <v>7003308</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119640341</v>
+        <v>119640334</v>
       </c>
       <c r="B6" t="n">
-        <v>91852</v>
+        <v>91884</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509269</v>
+        <v>509212</v>
       </c>
       <c r="R6" t="n">
-        <v>7003308</v>
+        <v>7003317</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119640353</v>
+        <v>119640326</v>
       </c>
       <c r="B7" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1278,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509374</v>
+        <v>509099</v>
       </c>
       <c r="R7" t="n">
-        <v>7003152</v>
+        <v>7003219</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1319,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>140-årig tallskog på sandig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1349,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119640317</v>
+        <v>119640345</v>
       </c>
       <c r="B8" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1389,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509191</v>
+        <v>509355</v>
       </c>
       <c r="R8" t="n">
-        <v>7003220</v>
+        <v>7003265</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119640319</v>
+        <v>119640317</v>
       </c>
       <c r="B9" t="n">
-        <v>79115</v>
+        <v>91856</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,21 +1468,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1500,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509150</v>
+        <v>509191</v>
       </c>
       <c r="R9" t="n">
-        <v>7003149</v>
+        <v>7003220</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,14 +1542,6 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
-        </is>
-      </c>
-      <c r="AN9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov skorstenshögstubbe</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1579,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119640331</v>
+        <v>119640316</v>
       </c>
       <c r="B10" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,21 +1579,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509112</v>
+        <v>509176</v>
       </c>
       <c r="R10" t="n">
-        <v>7003283</v>
+        <v>7003222</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1690,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119640350</v>
+        <v>119640346</v>
       </c>
       <c r="B11" t="n">
-        <v>91884</v>
+        <v>91852</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,25 +1686,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509371</v>
+        <v>509308</v>
       </c>
       <c r="R11" t="n">
-        <v>7003152</v>
+        <v>7003248</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1779,7 +1763,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>140-årig tallskog på sandig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1801,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119640322</v>
+        <v>119640348</v>
       </c>
       <c r="B12" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,21 +1801,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1841,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509105</v>
+        <v>509315</v>
       </c>
       <c r="R12" t="n">
-        <v>7003126</v>
+        <v>7003198</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1912,7 +1896,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119640318</v>
+        <v>119640313</v>
       </c>
       <c r="B13" t="n">
         <v>91834</v>
@@ -1952,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509193</v>
+        <v>509208</v>
       </c>
       <c r="R13" t="n">
-        <v>7003189</v>
+        <v>7003162</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119640320</v>
+        <v>119640351</v>
       </c>
       <c r="B14" t="n">
-        <v>91856</v>
+        <v>89252</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,25 +2019,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2047,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509134</v>
+        <v>509378</v>
       </c>
       <c r="R14" t="n">
-        <v>7003179</v>
+        <v>7003167</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2112,7 +2096,15 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på sandig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2134,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119640334</v>
+        <v>119640342</v>
       </c>
       <c r="B15" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2150,21 +2142,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2174,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509212</v>
+        <v>509303</v>
       </c>
       <c r="R15" t="n">
-        <v>7003317</v>
+        <v>7003323</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2467,7 +2459,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119640335</v>
+        <v>119640310</v>
       </c>
       <c r="B18" t="n">
         <v>91834</v>
@@ -2507,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509211</v>
+        <v>509021</v>
       </c>
       <c r="R18" t="n">
-        <v>7003306</v>
+        <v>7003112</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2578,10 +2570,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119640315</v>
+        <v>119640331</v>
       </c>
       <c r="B19" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2594,21 +2586,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2618,10 +2610,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509194</v>
+        <v>509112</v>
       </c>
       <c r="R19" t="n">
-        <v>7003235</v>
+        <v>7003283</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2689,10 +2681,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119640310</v>
+        <v>119640329</v>
       </c>
       <c r="B20" t="n">
-        <v>91834</v>
+        <v>78171</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2705,21 +2697,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2729,10 +2721,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509021</v>
+        <v>509119</v>
       </c>
       <c r="R20" t="n">
-        <v>7003112</v>
+        <v>7003280</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2779,6 +2771,14 @@
       <c r="AI20" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal lumpad talltopp</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2800,10 +2800,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119640328</v>
+        <v>119640347</v>
       </c>
       <c r="B21" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2816,21 +2816,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509119</v>
+        <v>509319</v>
       </c>
       <c r="R21" t="n">
-        <v>7003223</v>
+        <v>7003219</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119640303</v>
+        <v>119640322</v>
       </c>
       <c r="B22" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2927,21 +2927,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509034</v>
+        <v>509105</v>
       </c>
       <c r="R22" t="n">
-        <v>7002954</v>
+        <v>7003126</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119640316</v>
+        <v>119640306</v>
       </c>
       <c r="B23" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3038,21 +3038,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>509176</v>
+        <v>509070</v>
       </c>
       <c r="R23" t="n">
-        <v>7003222</v>
+        <v>7003029</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119640314</v>
+        <v>119640353</v>
       </c>
       <c r="B24" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3149,21 +3149,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>509280</v>
+        <v>509374</v>
       </c>
       <c r="R24" t="n">
-        <v>7003207</v>
+        <v>7003152</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på sandig morän med lav</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119640338</v>
+        <v>119640304</v>
       </c>
       <c r="B25" t="n">
-        <v>78171</v>
+        <v>91834</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3260,21 +3260,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509266</v>
+        <v>509047</v>
       </c>
       <c r="R25" t="n">
-        <v>7003365</v>
+        <v>7002984</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3334,14 +3334,6 @@
       <c r="AI25" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
-        </is>
-      </c>
-      <c r="AN25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal rest av tallåga</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3363,10 +3355,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119640352</v>
+        <v>119640311</v>
       </c>
       <c r="B26" t="n">
-        <v>78171</v>
+        <v>91884</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3379,21 +3371,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>5449</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,10 +3395,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509378</v>
+        <v>509147</v>
       </c>
       <c r="R26" t="n">
-        <v>7003167</v>
+        <v>7003106</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3452,15 +3444,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>140-årig tallskog på sandig morän med lav</t>
-        </is>
-      </c>
-      <c r="AN26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal hård tallåga</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3482,7 +3466,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119640343</v>
+        <v>119640320</v>
       </c>
       <c r="B27" t="n">
         <v>91856</v>
@@ -3522,10 +3506,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509352</v>
+        <v>509134</v>
       </c>
       <c r="R27" t="n">
-        <v>7003312</v>
+        <v>7003179</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3593,10 +3577,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119640347</v>
+        <v>119640314</v>
       </c>
       <c r="B28" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3609,21 +3593,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3633,10 +3617,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509319</v>
+        <v>509280</v>
       </c>
       <c r="R28" t="n">
-        <v>7003219</v>
+        <v>7003207</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3704,10 +3688,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119640346</v>
+        <v>119640350</v>
       </c>
       <c r="B29" t="n">
-        <v>91852</v>
+        <v>91884</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3716,25 +3700,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3744,10 +3728,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509308</v>
+        <v>509371</v>
       </c>
       <c r="R29" t="n">
-        <v>7003248</v>
+        <v>7003152</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3793,7 +3777,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på sandig morän med lav</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3815,10 +3799,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119640305</v>
+        <v>119640309</v>
       </c>
       <c r="B30" t="n">
-        <v>78171</v>
+        <v>91856</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3831,21 +3815,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3855,10 +3839,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509076</v>
+        <v>509034</v>
       </c>
       <c r="R30" t="n">
-        <v>7003011</v>
+        <v>7003097</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3905,14 +3889,6 @@
       <c r="AI30" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
-        </is>
-      </c>
-      <c r="AN30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal hård tallåga</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3934,7 +3910,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119640339</v>
+        <v>119640307</v>
       </c>
       <c r="B31" t="n">
         <v>91856</v>
@@ -3974,10 +3950,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509247</v>
+        <v>509057</v>
       </c>
       <c r="R31" t="n">
-        <v>7003393</v>
+        <v>7003066</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4045,10 +4021,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119640313</v>
+        <v>119640308</v>
       </c>
       <c r="B32" t="n">
-        <v>91834</v>
+        <v>89230</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4057,25 +4033,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4362</v>
+        <v>1596</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4085,10 +4061,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509208</v>
+        <v>509079</v>
       </c>
       <c r="R32" t="n">
-        <v>7003162</v>
+        <v>7003062</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4156,10 +4132,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119640306</v>
+        <v>119640338</v>
       </c>
       <c r="B33" t="n">
-        <v>91832</v>
+        <v>78171</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4172,21 +4148,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4196,10 +4172,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>509070</v>
+        <v>509266</v>
       </c>
       <c r="R33" t="n">
-        <v>7003029</v>
+        <v>7003365</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4246,6 +4222,14 @@
       <c r="AI33" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal rest av tallåga</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4267,10 +4251,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119640321</v>
+        <v>119640319</v>
       </c>
       <c r="B34" t="n">
-        <v>91834</v>
+        <v>79115</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4283,21 +4267,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4362</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4307,10 +4291,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>509129</v>
+        <v>509150</v>
       </c>
       <c r="R34" t="n">
-        <v>7003175</v>
+        <v>7003149</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4357,6 +4341,14 @@
       <c r="AI34" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov skorstenshögstubbe</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4378,10 +4370,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119640351</v>
+        <v>119640352</v>
       </c>
       <c r="B35" t="n">
-        <v>89252</v>
+        <v>78171</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4390,25 +4382,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4475,7 +4467,7 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>1 substratenheter</t>
+          <t>1 substratenheter # gammal hård tallåga</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4497,10 +4489,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119640325</v>
+        <v>119640305</v>
       </c>
       <c r="B36" t="n">
-        <v>89252</v>
+        <v>78171</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4509,25 +4501,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4537,10 +4529,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>509096</v>
+        <v>509076</v>
       </c>
       <c r="R36" t="n">
-        <v>7003215</v>
+        <v>7003011</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4587,6 +4579,14 @@
       <c r="AI36" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal hård tallåga</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4608,10 +4608,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119640311</v>
+        <v>119640333</v>
       </c>
       <c r="B37" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4624,21 +4624,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4648,10 +4648,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>509147</v>
+        <v>509193</v>
       </c>
       <c r="R37" t="n">
-        <v>7003106</v>
+        <v>7003303</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4719,10 +4719,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119640304</v>
+        <v>119640343</v>
       </c>
       <c r="B38" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4735,21 +4735,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4759,10 +4759,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509047</v>
+        <v>509352</v>
       </c>
       <c r="R38" t="n">
-        <v>7002984</v>
+        <v>7003312</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4830,10 +4830,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119640326</v>
+        <v>119640312</v>
       </c>
       <c r="B39" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4846,21 +4846,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4870,10 +4870,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509099</v>
+        <v>509178</v>
       </c>
       <c r="R39" t="n">
-        <v>7003219</v>
+        <v>7003099</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4941,10 +4941,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119640309</v>
+        <v>119640315</v>
       </c>
       <c r="B40" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4957,21 +4957,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>509034</v>
+        <v>509194</v>
       </c>
       <c r="R40" t="n">
-        <v>7003097</v>
+        <v>7003235</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5052,10 +5052,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119640312</v>
+        <v>119640318</v>
       </c>
       <c r="B41" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5068,21 +5068,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>509178</v>
+        <v>509193</v>
       </c>
       <c r="R41" t="n">
-        <v>7003099</v>
+        <v>7003189</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5163,10 +5163,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119640307</v>
+        <v>119640321</v>
       </c>
       <c r="B42" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5179,21 +5179,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>509057</v>
+        <v>509129</v>
       </c>
       <c r="R42" t="n">
-        <v>7003066</v>
+        <v>7003175</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5274,10 +5274,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119640342</v>
+        <v>119640325</v>
       </c>
       <c r="B43" t="n">
-        <v>91834</v>
+        <v>89252</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5286,25 +5286,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>509303</v>
+        <v>509096</v>
       </c>
       <c r="R43" t="n">
-        <v>7003323</v>
+        <v>7003215</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5385,10 +5385,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119640308</v>
+        <v>119640335</v>
       </c>
       <c r="B44" t="n">
-        <v>89230</v>
+        <v>91834</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5397,25 +5397,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1596</v>
+        <v>4362</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5425,10 +5425,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>509079</v>
+        <v>509211</v>
       </c>
       <c r="R44" t="n">
-        <v>7003062</v>
+        <v>7003306</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 27907-2024 artfynd.xlsx
+++ b/artfynd/A 27907-2024 artfynd.xlsx
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119640317</v>
+        <v>119640316</v>
       </c>
       <c r="B9" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,21 +1468,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509191</v>
+        <v>509176</v>
       </c>
       <c r="R9" t="n">
-        <v>7003220</v>
+        <v>7003222</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119640316</v>
+        <v>119640346</v>
       </c>
       <c r="B10" t="n">
-        <v>91884</v>
+        <v>91852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,25 +1575,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509176</v>
+        <v>509308</v>
       </c>
       <c r="R10" t="n">
-        <v>7003222</v>
+        <v>7003248</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119640346</v>
+        <v>119640317</v>
       </c>
       <c r="B11" t="n">
-        <v>91852</v>
+        <v>91856</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,25 +1686,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509308</v>
+        <v>509191</v>
       </c>
       <c r="R11" t="n">
-        <v>7003248</v>
+        <v>7003220</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -3577,10 +3577,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119640314</v>
+        <v>119640309</v>
       </c>
       <c r="B28" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3593,21 +3593,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509280</v>
+        <v>509034</v>
       </c>
       <c r="R28" t="n">
-        <v>7003207</v>
+        <v>7003097</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3688,10 +3688,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119640350</v>
+        <v>119640307</v>
       </c>
       <c r="B29" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3704,21 +3704,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509371</v>
+        <v>509057</v>
       </c>
       <c r="R29" t="n">
-        <v>7003152</v>
+        <v>7003066</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>140-årig tallskog på sandig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3799,10 +3799,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119640309</v>
+        <v>119640314</v>
       </c>
       <c r="B30" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3815,21 +3815,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3839,10 +3839,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509034</v>
+        <v>509280</v>
       </c>
       <c r="R30" t="n">
-        <v>7003097</v>
+        <v>7003207</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3910,10 +3910,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119640307</v>
+        <v>119640350</v>
       </c>
       <c r="B31" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3926,21 +3926,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509057</v>
+        <v>509371</v>
       </c>
       <c r="R31" t="n">
-        <v>7003066</v>
+        <v>7003152</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på sandig morän med lav</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4021,10 +4021,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119640308</v>
+        <v>119640338</v>
       </c>
       <c r="B32" t="n">
-        <v>89230</v>
+        <v>78171</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4033,25 +4033,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1596</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509079</v>
+        <v>509266</v>
       </c>
       <c r="R32" t="n">
-        <v>7003062</v>
+        <v>7003365</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4111,6 +4111,14 @@
       <c r="AI32" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal rest av tallåga</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4132,10 +4140,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119640338</v>
+        <v>119640308</v>
       </c>
       <c r="B33" t="n">
-        <v>78171</v>
+        <v>89230</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4144,25 +4152,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>1596</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4172,10 +4180,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>509266</v>
+        <v>509079</v>
       </c>
       <c r="R33" t="n">
-        <v>7003365</v>
+        <v>7003062</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4222,14 +4230,6 @@
       <c r="AI33" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
-        </is>
-      </c>
-      <c r="AN33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal rest av tallåga</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4608,7 +4608,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119640333</v>
+        <v>119640343</v>
       </c>
       <c r="B37" t="n">
         <v>91856</v>
@@ -4648,10 +4648,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>509193</v>
+        <v>509352</v>
       </c>
       <c r="R37" t="n">
-        <v>7003303</v>
+        <v>7003312</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4719,10 +4719,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119640343</v>
+        <v>119640312</v>
       </c>
       <c r="B38" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4735,21 +4735,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4759,10 +4759,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509352</v>
+        <v>509178</v>
       </c>
       <c r="R38" t="n">
-        <v>7003312</v>
+        <v>7003099</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4830,7 +4830,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119640312</v>
+        <v>119640315</v>
       </c>
       <c r="B39" t="n">
         <v>91832</v>
@@ -4870,10 +4870,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509178</v>
+        <v>509194</v>
       </c>
       <c r="R39" t="n">
-        <v>7003099</v>
+        <v>7003235</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4941,10 +4941,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119640315</v>
+        <v>119640318</v>
       </c>
       <c r="B40" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4957,21 +4957,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>509194</v>
+        <v>509193</v>
       </c>
       <c r="R40" t="n">
-        <v>7003235</v>
+        <v>7003189</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5052,10 +5052,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119640318</v>
+        <v>119640333</v>
       </c>
       <c r="B41" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5068,21 +5068,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5095,7 +5095,7 @@
         <v>509193</v>
       </c>
       <c r="R41" t="n">
-        <v>7003189</v>
+        <v>7003303</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 27907-2024 artfynd.xlsx
+++ b/artfynd/A 27907-2024 artfynd.xlsx
@@ -3355,10 +3355,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119640311</v>
+        <v>119640320</v>
       </c>
       <c r="B26" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3371,21 +3371,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509147</v>
+        <v>509134</v>
       </c>
       <c r="R26" t="n">
-        <v>7003106</v>
+        <v>7003179</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119640320</v>
+        <v>119640311</v>
       </c>
       <c r="B27" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3482,21 +3482,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3506,10 +3506,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509134</v>
+        <v>509147</v>
       </c>
       <c r="R27" t="n">
-        <v>7003179</v>
+        <v>7003106</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4608,7 +4608,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119640343</v>
+        <v>119640333</v>
       </c>
       <c r="B37" t="n">
         <v>91856</v>
@@ -4648,10 +4648,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>509352</v>
+        <v>509193</v>
       </c>
       <c r="R37" t="n">
-        <v>7003312</v>
+        <v>7003303</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4719,10 +4719,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119640312</v>
+        <v>119640343</v>
       </c>
       <c r="B38" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4735,21 +4735,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4759,10 +4759,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509178</v>
+        <v>509352</v>
       </c>
       <c r="R38" t="n">
-        <v>7003099</v>
+        <v>7003312</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4830,7 +4830,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119640315</v>
+        <v>119640312</v>
       </c>
       <c r="B39" t="n">
         <v>91832</v>
@@ -4870,10 +4870,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509194</v>
+        <v>509178</v>
       </c>
       <c r="R39" t="n">
-        <v>7003235</v>
+        <v>7003099</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4941,10 +4941,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119640318</v>
+        <v>119640315</v>
       </c>
       <c r="B40" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4957,21 +4957,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>509193</v>
+        <v>509194</v>
       </c>
       <c r="R40" t="n">
-        <v>7003189</v>
+        <v>7003235</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5052,10 +5052,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119640333</v>
+        <v>119640318</v>
       </c>
       <c r="B41" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5068,21 +5068,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5095,7 +5095,7 @@
         <v>509193</v>
       </c>
       <c r="R41" t="n">
-        <v>7003303</v>
+        <v>7003189</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 27907-2024 artfynd.xlsx
+++ b/artfynd/A 27907-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119640303</v>
+        <v>119640305</v>
       </c>
       <c r="B2" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509034</v>
+        <v>509076</v>
       </c>
       <c r="R2" t="n">
-        <v>7002954</v>
+        <v>7003011</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,6 +760,14 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal hård tallåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119640339</v>
+        <v>119640329</v>
       </c>
       <c r="B3" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +800,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509247</v>
+        <v>509119</v>
       </c>
       <c r="R3" t="n">
-        <v>7003393</v>
+        <v>7003280</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,6 +874,14 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal lumpad talltopp</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119640328</v>
+        <v>119640338</v>
       </c>
       <c r="B4" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509119</v>
+        <v>509266</v>
       </c>
       <c r="R4" t="n">
-        <v>7003223</v>
+        <v>7003365</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,6 +988,14 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal rest av tallåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,37 +1017,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119640341</v>
+        <v>119640352</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509269</v>
+        <v>509378</v>
       </c>
       <c r="R5" t="n">
-        <v>7003308</v>
+        <v>7003167</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,7 +1101,15 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på sandig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal hård tallåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1119,37 +1131,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119640334</v>
+        <v>119640308</v>
       </c>
       <c r="B6" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90674</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>1596</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509212</v>
+        <v>509079</v>
       </c>
       <c r="R6" t="n">
-        <v>7003317</v>
+        <v>7003062</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,19 +1237,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119640326</v>
+        <v>119640307</v>
       </c>
       <c r="B7" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1270,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509099</v>
+        <v>509057</v>
       </c>
       <c r="R7" t="n">
-        <v>7003219</v>
+        <v>7003066</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,37 +1343,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119640345</v>
+        <v>119640309</v>
       </c>
       <c r="B8" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1381,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509355</v>
+        <v>509034</v>
       </c>
       <c r="R8" t="n">
-        <v>7003265</v>
+        <v>7003097</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,37 +1449,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119640316</v>
+        <v>119640317</v>
       </c>
       <c r="B9" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509176</v>
+        <v>509191</v>
       </c>
       <c r="R9" t="n">
-        <v>7003222</v>
+        <v>7003220</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,37 +1555,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119640346</v>
+        <v>119640320</v>
       </c>
       <c r="B10" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1603,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509308</v>
+        <v>509134</v>
       </c>
       <c r="R10" t="n">
-        <v>7003248</v>
+        <v>7003179</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,19 +1661,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119640317</v>
+        <v>119640323</v>
       </c>
       <c r="B11" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1714,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509191</v>
+        <v>509110</v>
       </c>
       <c r="R11" t="n">
-        <v>7003220</v>
+        <v>7003127</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,19 +1767,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119640348</v>
+        <v>119640326</v>
       </c>
       <c r="B12" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1825,10 +1802,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509315</v>
+        <v>509099</v>
       </c>
       <c r="R12" t="n">
-        <v>7003198</v>
+        <v>7003219</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,37 +1873,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119640313</v>
+        <v>119640331</v>
       </c>
       <c r="B13" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1936,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509208</v>
+        <v>509112</v>
       </c>
       <c r="R13" t="n">
-        <v>7003162</v>
+        <v>7003283</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,15 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119640351</v>
+        <v>119640333</v>
       </c>
       <c r="B14" t="n">
-        <v>89252</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,21 +1990,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2047,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509378</v>
+        <v>509193</v>
       </c>
       <c r="R14" t="n">
-        <v>7003167</v>
+        <v>7003303</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2096,15 +2063,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>140-årig tallskog på sandig morän med lav</t>
-        </is>
-      </c>
-      <c r="AN14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2126,37 +2085,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119640342</v>
+        <v>119640339</v>
       </c>
       <c r="B15" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509303</v>
+        <v>509247</v>
       </c>
       <c r="R15" t="n">
-        <v>7003323</v>
+        <v>7003393</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2237,19 +2191,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119640323</v>
+        <v>119640343</v>
       </c>
       <c r="B16" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2277,10 +2226,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509110</v>
+        <v>509352</v>
       </c>
       <c r="R16" t="n">
-        <v>7003127</v>
+        <v>7003312</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2348,37 +2297,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119640332</v>
+        <v>119640347</v>
       </c>
       <c r="B17" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2388,10 +2332,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509129</v>
+        <v>509319</v>
       </c>
       <c r="R17" t="n">
-        <v>7003296</v>
+        <v>7003219</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2459,37 +2403,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119640310</v>
+        <v>119640348</v>
       </c>
       <c r="B18" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2499,10 +2438,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509021</v>
+        <v>509315</v>
       </c>
       <c r="R18" t="n">
-        <v>7003112</v>
+        <v>7003198</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2570,15 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119640331</v>
+        <v>119640306</v>
       </c>
       <c r="B19" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2586,21 +2520,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2610,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509112</v>
+        <v>509070</v>
       </c>
       <c r="R19" t="n">
-        <v>7003283</v>
+        <v>7003029</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2681,15 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119640329</v>
+        <v>119640312</v>
       </c>
       <c r="B20" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,21 +2626,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2721,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509119</v>
+        <v>509178</v>
       </c>
       <c r="R20" t="n">
-        <v>7003280</v>
+        <v>7003099</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2771,14 +2700,6 @@
       <c r="AI20" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
-        </is>
-      </c>
-      <c r="AN20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal lumpad talltopp</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2800,15 +2721,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119640347</v>
+        <v>119640315</v>
       </c>
       <c r="B21" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2816,21 +2732,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2840,10 +2756,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509319</v>
+        <v>509194</v>
       </c>
       <c r="R21" t="n">
-        <v>7003219</v>
+        <v>7003235</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2911,15 +2827,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119640322</v>
+        <v>119640345</v>
       </c>
       <c r="B22" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2927,21 +2838,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2951,10 +2862,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509105</v>
+        <v>509355</v>
       </c>
       <c r="R22" t="n">
-        <v>7003126</v>
+        <v>7003265</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3022,15 +2933,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119640306</v>
+        <v>119640304</v>
       </c>
       <c r="B23" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,21 +2944,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3062,10 +2968,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>509070</v>
+        <v>509047</v>
       </c>
       <c r="R23" t="n">
-        <v>7003029</v>
+        <v>7002984</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3133,15 +3039,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119640353</v>
+        <v>119640310</v>
       </c>
       <c r="B24" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3173,10 +3074,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>509374</v>
+        <v>509021</v>
       </c>
       <c r="R24" t="n">
-        <v>7003152</v>
+        <v>7003112</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3222,7 +3123,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>140-årig tallskog på sandig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3244,15 +3145,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119640304</v>
+        <v>119640313</v>
       </c>
       <c r="B25" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3284,10 +3180,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509047</v>
+        <v>509208</v>
       </c>
       <c r="R25" t="n">
-        <v>7002984</v>
+        <v>7003162</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3355,15 +3251,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119640320</v>
+        <v>119640318</v>
       </c>
       <c r="B26" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3371,21 +3262,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3395,10 +3286,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509134</v>
+        <v>509193</v>
       </c>
       <c r="R26" t="n">
-        <v>7003179</v>
+        <v>7003189</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3466,15 +3357,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119640311</v>
+        <v>119640321</v>
       </c>
       <c r="B27" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3482,21 +3368,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3506,10 +3392,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509147</v>
+        <v>509129</v>
       </c>
       <c r="R27" t="n">
-        <v>7003106</v>
+        <v>7003175</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3577,15 +3463,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119640309</v>
+        <v>119640322</v>
       </c>
       <c r="B28" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3593,21 +3474,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3617,10 +3498,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509034</v>
+        <v>509105</v>
       </c>
       <c r="R28" t="n">
-        <v>7003097</v>
+        <v>7003126</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3688,15 +3569,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119640307</v>
+        <v>119640328</v>
       </c>
       <c r="B29" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3704,21 +3580,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3728,10 +3604,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509057</v>
+        <v>509119</v>
       </c>
       <c r="R29" t="n">
-        <v>7003066</v>
+        <v>7003223</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3799,15 +3675,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119640314</v>
+        <v>119640332</v>
       </c>
       <c r="B30" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3815,21 +3686,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3839,10 +3710,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509280</v>
+        <v>509129</v>
       </c>
       <c r="R30" t="n">
-        <v>7003207</v>
+        <v>7003296</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3910,15 +3781,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119640350</v>
+        <v>119640335</v>
       </c>
       <c r="B31" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3926,21 +3792,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3950,10 +3816,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509371</v>
+        <v>509211</v>
       </c>
       <c r="R31" t="n">
-        <v>7003152</v>
+        <v>7003306</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3999,7 +3865,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>140-årig tallskog på sandig morän med lav</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4021,15 +3887,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119640338</v>
+        <v>119640342</v>
       </c>
       <c r="B32" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4037,21 +3898,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4061,10 +3922,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509266</v>
+        <v>509303</v>
       </c>
       <c r="R32" t="n">
-        <v>7003365</v>
+        <v>7003323</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4111,14 +3972,6 @@
       <c r="AI32" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
-        </is>
-      </c>
-      <c r="AN32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal rest av tallåga</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4140,37 +3993,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119640308</v>
+        <v>119640353</v>
       </c>
       <c r="B33" t="n">
-        <v>89230</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1596</v>
+        <v>4362</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4180,10 +4028,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>509079</v>
+        <v>509374</v>
       </c>
       <c r="R33" t="n">
-        <v>7003062</v>
+        <v>7003152</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4229,7 +4077,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på sandig morän med lav</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4251,15 +4099,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119640319</v>
+        <v>62023322</v>
       </c>
       <c r="B34" t="n">
-        <v>79115</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4267,34 +4110,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, öster om, Jmt</t>
+          <t>Stugusjön, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>509150</v>
+        <v>509126</v>
       </c>
       <c r="R34" t="n">
-        <v>7003149</v>
+        <v>7003320</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4321,12 +4164,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2016-10-26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2016-10-26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4340,7 +4183,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AN34" t="n">
@@ -4348,37 +4191,28 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov skorstenshögstubbe</t>
+          <t>1 substratenheter</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Johan Kjetselberg, Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119640352</v>
+        <v>119640341</v>
       </c>
       <c r="B35" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4386,21 +4220,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4410,10 +4244,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>509378</v>
+        <v>509269</v>
       </c>
       <c r="R35" t="n">
-        <v>7003167</v>
+        <v>7003308</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4459,15 +4293,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>140-årig tallskog på sandig morän med lav</t>
-        </is>
-      </c>
-      <c r="AN35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal hård tallåga</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4489,15 +4315,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119640305</v>
+        <v>119640346</v>
       </c>
       <c r="B36" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4505,21 +4326,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4529,10 +4350,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>509076</v>
+        <v>509308</v>
       </c>
       <c r="R36" t="n">
-        <v>7003011</v>
+        <v>7003248</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4579,14 +4400,6 @@
       <c r="AI36" t="inlineStr">
         <is>
           <t>140-årig tallskog på småblockig morän med lav</t>
-        </is>
-      </c>
-      <c r="AN36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal hård tallåga</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4608,37 +4421,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119640333</v>
+        <v>119640325</v>
       </c>
       <c r="B37" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4648,10 +4456,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>509193</v>
+        <v>509096</v>
       </c>
       <c r="R37" t="n">
-        <v>7003303</v>
+        <v>7003215</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4719,37 +4527,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119640343</v>
+        <v>119640351</v>
       </c>
       <c r="B38" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4759,10 +4562,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509352</v>
+        <v>509378</v>
       </c>
       <c r="R38" t="n">
-        <v>7003312</v>
+        <v>7003167</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4808,7 +4611,15 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
+          <t>140-årig tallskog på sandig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4830,15 +4641,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119640312</v>
+        <v>106082182</v>
       </c>
       <c r="B39" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4846,37 +4652,53 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Orrviktjärnen, öster om, Jmt</t>
+          <t>Lillsjöhögen, Östersund, Stugusjöån, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509178</v>
+        <v>509332</v>
       </c>
       <c r="R39" t="n">
-        <v>7003099</v>
+        <v>7003124</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4900,12 +4722,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2022-07-11</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4916,40 +4738,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Tobias Nykänen</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119640315</v>
+        <v>119640319</v>
       </c>
       <c r="B40" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4957,21 +4765,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4361</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4981,10 +4789,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>509194</v>
+        <v>509150</v>
       </c>
       <c r="R40" t="n">
-        <v>7003235</v>
+        <v>7003149</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5033,6 +4841,14 @@
           <t>140-årig tallskog på småblockig morän med lav</t>
         </is>
       </c>
+      <c r="AN40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov skorstenshögstubbe</t>
+        </is>
+      </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
@@ -5045,450 +4861,6 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>119640318</v>
-      </c>
-      <c r="B41" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>4362</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Blå taggsvamp</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Hydnellum caeruleum</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Orrviktjärnen, öster om, Jmt</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>509193</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7003189</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
-        </is>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>119640321</v>
-      </c>
-      <c r="B42" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>4362</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Blå taggsvamp</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Hydnellum caeruleum</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Orrviktjärnen, öster om, Jmt</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>509129</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7003175</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
-        </is>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>119640325</v>
-      </c>
-      <c r="B43" t="n">
-        <v>89252</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>6276</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Goliatmusseron</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Tricholoma matsutake</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Orrviktjärnen, öster om, Jmt</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>509096</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7003215</v>
-      </c>
-      <c r="S43" t="n">
-        <v>10</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
-        </is>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>119640335</v>
-      </c>
-      <c r="B44" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>4362</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Blå taggsvamp</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Hydnellum caeruleum</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Orrviktjärnen, öster om, Jmt</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>509211</v>
-      </c>
-      <c r="R44" t="n">
-        <v>7003306</v>
-      </c>
-      <c r="S44" t="n">
-        <v>10</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>140-årig tallskog på småblockig morän med lav</t>
-        </is>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 27907-2024 artfynd.xlsx
+++ b/artfynd/A 27907-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640305</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640329</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640338</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640352</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1234,6 +1259,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640308</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,6 +1370,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640307</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1446,6 +1481,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640309</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1552,6 +1592,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640317</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1658,6 +1703,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640320</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1764,6 +1814,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640323</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1870,6 +1925,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640326</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1976,6 +2036,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640331</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2082,6 +2147,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640333</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2188,6 +2258,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640339</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2294,6 +2369,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640343</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2400,6 +2480,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640347</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2506,6 +2591,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640348</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2612,6 +2702,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640306</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2718,6 +2813,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640312</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2824,6 +2924,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640315</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2930,6 +3035,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640345</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3036,6 +3146,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640304</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3142,6 +3257,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640310</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3248,6 +3368,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640313</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3354,6 +3479,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640318</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3460,6 +3590,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640321</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3566,6 +3701,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640322</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3672,6 +3812,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640328</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3778,6 +3923,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640332</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3884,6 +4034,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640335</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3990,6 +4145,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640342</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4096,6 +4256,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640353</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4206,6 +4371,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62023322</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4312,6 +4482,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640341</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4418,6 +4593,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640346</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4524,6 +4704,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640325</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4638,6 +4823,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640351</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4751,6 +4941,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106082182</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4865,8 +5060,54 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119640319</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>